--- a/output/yearly_population_iteration_13_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_13_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4798</v>
+        <v>6514</v>
       </c>
       <c r="C2" t="n">
-        <v>8376</v>
+        <v>7508</v>
       </c>
       <c r="D2" t="n">
-        <v>24805</v>
+        <v>26333</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2494</v>
+        <v>3530</v>
       </c>
       <c r="C3" t="n">
-        <v>5999</v>
+        <v>4966</v>
       </c>
       <c r="D3" t="n">
-        <v>15566</v>
+        <v>16787</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2172</v>
+        <v>2641</v>
       </c>
       <c r="C4" t="n">
-        <v>3375</v>
+        <v>5541</v>
       </c>
       <c r="D4" t="n">
-        <v>9111</v>
+        <v>7559</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1456</v>
+        <v>1758</v>
       </c>
       <c r="C5" t="n">
-        <v>2939</v>
+        <v>4121</v>
       </c>
       <c r="D5" t="n">
-        <v>3663</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>873</v>
+        <v>975</v>
       </c>
       <c r="C6" t="n">
-        <v>2149</v>
+        <v>2482</v>
       </c>
       <c r="D6" t="n">
-        <v>1425</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>420</v>
+        <v>468</v>
       </c>
       <c r="C7" t="n">
-        <v>1450</v>
+        <v>1437</v>
       </c>
       <c r="D7" t="n">
-        <v>688</v>
+        <v>638</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="C8" t="n">
-        <v>742</v>
+        <v>733</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10">
@@ -898,7 +898,7 @@
         <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D13" t="n">
         <v>125</v>
@@ -951,10 +951,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -982,7 +982,7 @@
         <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5828</v>
+        <v>6488</v>
       </c>
       <c r="C2" t="n">
-        <v>6864</v>
+        <v>12261</v>
       </c>
       <c r="D2" t="n">
-        <v>25546</v>
+        <v>28786</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2861</v>
+        <v>3985</v>
       </c>
       <c r="C3" t="n">
-        <v>6248</v>
+        <v>5399</v>
       </c>
       <c r="D3" t="n">
-        <v>15825</v>
+        <v>16957</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1987</v>
+        <v>2590</v>
       </c>
       <c r="C4" t="n">
-        <v>4614</v>
+        <v>5144</v>
       </c>
       <c r="D4" t="n">
-        <v>9949</v>
+        <v>8762</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1584</v>
+        <v>1897</v>
       </c>
       <c r="C5" t="n">
-        <v>3058</v>
+        <v>4663</v>
       </c>
       <c r="D5" t="n">
-        <v>4405</v>
+        <v>3268</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1030</v>
+        <v>1208</v>
       </c>
       <c r="C6" t="n">
-        <v>2498</v>
+        <v>3212</v>
       </c>
       <c r="D6" t="n">
-        <v>1770</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>555</v>
+        <v>614</v>
       </c>
       <c r="C7" t="n">
-        <v>1757</v>
+        <v>1893</v>
       </c>
       <c r="D7" t="n">
-        <v>796</v>
+        <v>699</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="C8" t="n">
-        <v>1060</v>
+        <v>1043</v>
       </c>
       <c r="D8" t="n">
-        <v>468</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C9" t="n">
-        <v>517</v>
+        <v>502</v>
       </c>
       <c r="D9" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6219</v>
+        <v>7100</v>
       </c>
       <c r="C2" t="n">
-        <v>6004</v>
+        <v>9782</v>
       </c>
       <c r="D2" t="n">
-        <v>25270</v>
+        <v>30265</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3327</v>
+        <v>4095</v>
       </c>
       <c r="C3" t="n">
-        <v>5754</v>
+        <v>7357</v>
       </c>
       <c r="D3" t="n">
-        <v>16031</v>
+        <v>17358</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2024</v>
+        <v>2692</v>
       </c>
       <c r="C4" t="n">
-        <v>5270</v>
+        <v>5152</v>
       </c>
       <c r="D4" t="n">
-        <v>10453</v>
+        <v>9754</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1565</v>
+        <v>1960</v>
       </c>
       <c r="C5" t="n">
-        <v>3652</v>
+        <v>4729</v>
       </c>
       <c r="D5" t="n">
-        <v>5122</v>
+        <v>3928</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1150</v>
+        <v>1356</v>
       </c>
       <c r="C6" t="n">
-        <v>2716</v>
+        <v>3795</v>
       </c>
       <c r="D6" t="n">
-        <v>2108</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>675</v>
+        <v>765</v>
       </c>
       <c r="C7" t="n">
-        <v>2051</v>
+        <v>2416</v>
       </c>
       <c r="D7" t="n">
-        <v>931</v>
+        <v>763</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>330</v>
+        <v>355</v>
       </c>
       <c r="C8" t="n">
-        <v>1336</v>
+        <v>1373</v>
       </c>
       <c r="D8" t="n">
-        <v>503</v>
+        <v>488</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="C9" t="n">
-        <v>734</v>
+        <v>713</v>
       </c>
       <c r="D9" t="n">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D11" t="n">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5635</v>
+        <v>6561</v>
       </c>
       <c r="C2" t="n">
-        <v>3986</v>
+        <v>6573</v>
       </c>
       <c r="D2" t="n">
-        <v>20629</v>
+        <v>24878</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3907</v>
+        <v>4910</v>
       </c>
       <c r="C3" t="n">
-        <v>8364</v>
+        <v>10342</v>
       </c>
       <c r="D3" t="n">
-        <v>18087</v>
+        <v>18899</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1446</v>
+        <v>1811</v>
       </c>
       <c r="C4" t="n">
-        <v>6541</v>
+        <v>7457</v>
       </c>
       <c r="D4" t="n">
-        <v>10415</v>
+        <v>9138</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1062</v>
+        <v>1252</v>
       </c>
       <c r="C5" t="n">
-        <v>2661</v>
+        <v>3719</v>
       </c>
       <c r="D5" t="n">
-        <v>3491</v>
+        <v>2603</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>623</v>
+        <v>706</v>
       </c>
       <c r="C6" t="n">
-        <v>2009</v>
+        <v>2367</v>
       </c>
       <c r="D6" t="n">
-        <v>912</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>304</v>
+        <v>328</v>
       </c>
       <c r="C7" t="n">
-        <v>1309</v>
+        <v>1345</v>
       </c>
       <c r="D7" t="n">
-        <v>492</v>
+        <v>478</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="C8" t="n">
-        <v>719</v>
+        <v>698</v>
       </c>
       <c r="D8" t="n">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="D9" t="n">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D10" t="n">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3353</v>
+        <v>3988</v>
       </c>
       <c r="C2" t="n">
-        <v>2005</v>
+        <v>2720</v>
       </c>
       <c r="D2" t="n">
-        <v>14606</v>
+        <v>17631</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4023</v>
+        <v>4871</v>
       </c>
       <c r="C3" t="n">
-        <v>5704</v>
+        <v>7797</v>
       </c>
       <c r="D3" t="n">
-        <v>17555</v>
+        <v>18623</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2097</v>
+        <v>2605</v>
       </c>
       <c r="C4" t="n">
-        <v>7468</v>
+        <v>8873</v>
       </c>
       <c r="D4" t="n">
-        <v>11376</v>
+        <v>10534</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1166</v>
+        <v>1396</v>
       </c>
       <c r="C5" t="n">
-        <v>4409</v>
+        <v>5399</v>
       </c>
       <c r="D5" t="n">
-        <v>4416</v>
+        <v>3389</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>750</v>
+        <v>847</v>
       </c>
       <c r="C6" t="n">
-        <v>2368</v>
+        <v>2991</v>
       </c>
       <c r="D6" t="n">
-        <v>1175</v>
+        <v>938</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="C7" t="n">
-        <v>1622</v>
+        <v>1730</v>
       </c>
       <c r="D7" t="n">
-        <v>540</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C8" t="n">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="D8" t="n">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D10" t="n">
         <v>211</v>
@@ -2153,7 +2153,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D11" t="n">
         <v>166</v>
@@ -2167,10 +2167,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3280</v>
+        <v>3748</v>
       </c>
       <c r="C2" t="n">
-        <v>3714</v>
+        <v>4741</v>
       </c>
       <c r="D2" t="n">
-        <v>13854</v>
+        <v>14845</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3133</v>
+        <v>3778</v>
       </c>
       <c r="C3" t="n">
-        <v>3439</v>
+        <v>4746</v>
       </c>
       <c r="D3" t="n">
-        <v>15922</v>
+        <v>17377</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2545</v>
+        <v>3096</v>
       </c>
       <c r="C4" t="n">
-        <v>6415</v>
+        <v>8151</v>
       </c>
       <c r="D4" t="n">
-        <v>12097</v>
+        <v>11432</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1393</v>
+        <v>1691</v>
       </c>
       <c r="C5" t="n">
-        <v>5814</v>
+        <v>7006</v>
       </c>
       <c r="D5" t="n">
-        <v>5417</v>
+        <v>4452</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>856</v>
+        <v>988</v>
       </c>
       <c r="C6" t="n">
-        <v>3327</v>
+        <v>4048</v>
       </c>
       <c r="D6" t="n">
-        <v>1657</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>421</v>
+        <v>460</v>
       </c>
       <c r="C7" t="n">
-        <v>1973</v>
+        <v>2302</v>
       </c>
       <c r="D7" t="n">
-        <v>627</v>
+        <v>581</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="C8" t="n">
-        <v>1224</v>
+        <v>1260</v>
       </c>
       <c r="D8" t="n">
-        <v>368</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>616</v>
+        <v>599</v>
       </c>
       <c r="D9" t="n">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2495,7 +2495,7 @@
         <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1906</v>
+        <v>2213</v>
       </c>
       <c r="C2" t="n">
-        <v>1651</v>
+        <v>2186</v>
       </c>
       <c r="D2" t="n">
-        <v>9564</v>
+        <v>10248</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3055</v>
+        <v>3667</v>
       </c>
       <c r="C3" t="n">
-        <v>3416</v>
+        <v>4592</v>
       </c>
       <c r="D3" t="n">
-        <v>15308</v>
+        <v>16676</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2827</v>
+        <v>3400</v>
       </c>
       <c r="C4" t="n">
-        <v>5901</v>
+        <v>7619</v>
       </c>
       <c r="D4" t="n">
-        <v>12677</v>
+        <v>12246</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1482</v>
+        <v>1752</v>
       </c>
       <c r="C5" t="n">
-        <v>6710</v>
+        <v>8320</v>
       </c>
       <c r="D5" t="n">
-        <v>5827</v>
+        <v>4810</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>752</v>
+        <v>835</v>
       </c>
       <c r="C6" t="n">
-        <v>4189</v>
+        <v>4894</v>
       </c>
       <c r="D6" t="n">
-        <v>1608</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="C7" t="n">
-        <v>2157</v>
+        <v>2373</v>
       </c>
       <c r="D7" t="n">
-        <v>622</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>999</v>
+        <v>982</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2928</v>
+        <v>3122</v>
       </c>
       <c r="C2" t="n">
-        <v>5497</v>
+        <v>4220</v>
       </c>
       <c r="D2" t="n">
-        <v>8557</v>
+        <v>14591</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2191</v>
+        <v>2618</v>
       </c>
       <c r="C3" t="n">
-        <v>2274</v>
+        <v>3096</v>
       </c>
       <c r="D3" t="n">
-        <v>13574</v>
+        <v>14681</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2560</v>
+        <v>3103</v>
       </c>
       <c r="C4" t="n">
-        <v>4594</v>
+        <v>6080</v>
       </c>
       <c r="D4" t="n">
-        <v>12720</v>
+        <v>12596</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1819</v>
+        <v>2143</v>
       </c>
       <c r="C5" t="n">
-        <v>6254</v>
+        <v>7910</v>
       </c>
       <c r="D5" t="n">
-        <v>6702</v>
+        <v>5852</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>958</v>
+        <v>1081</v>
       </c>
       <c r="C6" t="n">
-        <v>5303</v>
+        <v>6344</v>
       </c>
       <c r="D6" t="n">
-        <v>2194</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="C7" t="n">
-        <v>3054</v>
+        <v>3431</v>
       </c>
       <c r="D7" t="n">
-        <v>757</v>
+        <v>671</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>1460</v>
+        <v>1505</v>
       </c>
       <c r="D8" t="n">
-        <v>413</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>544</v>
+        <v>517</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3103,7 +3103,7 @@
         <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3145,7 +3145,7 @@
         <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -3173,7 +3173,7 @@
         <v>74</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1915</v>
+        <v>2332</v>
       </c>
       <c r="C2" t="n">
-        <v>3532</v>
+        <v>3219</v>
       </c>
       <c r="D2" t="n">
-        <v>6606</v>
+        <v>11424</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2136</v>
+        <v>2438</v>
       </c>
       <c r="C3" t="n">
-        <v>3311</v>
+        <v>3213</v>
       </c>
       <c r="D3" t="n">
-        <v>12171</v>
+        <v>13871</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2233</v>
+        <v>2727</v>
       </c>
       <c r="C4" t="n">
-        <v>3628</v>
+        <v>4896</v>
       </c>
       <c r="D4" t="n">
-        <v>12700</v>
+        <v>12614</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1973</v>
+        <v>2330</v>
       </c>
       <c r="C5" t="n">
-        <v>5726</v>
+        <v>7381</v>
       </c>
       <c r="D5" t="n">
-        <v>7255</v>
+        <v>6563</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1127</v>
+        <v>1269</v>
       </c>
       <c r="C6" t="n">
-        <v>5835</v>
+        <v>7092</v>
       </c>
       <c r="D6" t="n">
-        <v>2664</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="C7" t="n">
-        <v>3857</v>
+        <v>4378</v>
       </c>
       <c r="D7" t="n">
-        <v>864</v>
+        <v>764</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>1880</v>
+        <v>1959</v>
       </c>
       <c r="D8" t="n">
-        <v>438</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>666</v>
+        <v>605</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3442,7 +3442,7 @@
         <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -3470,7 +3470,7 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3020</v>
+        <v>3834</v>
       </c>
       <c r="C2" t="n">
-        <v>5103</v>
+        <v>7966</v>
       </c>
       <c r="D2" t="n">
-        <v>14433</v>
+        <v>15800</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1725</v>
+        <v>2019</v>
       </c>
       <c r="C3" t="n">
-        <v>3040</v>
+        <v>2855</v>
       </c>
       <c r="D3" t="n">
-        <v>10660</v>
+        <v>12689</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1909</v>
+        <v>2281</v>
       </c>
       <c r="C4" t="n">
-        <v>3409</v>
+        <v>4067</v>
       </c>
       <c r="D4" t="n">
-        <v>12232</v>
+        <v>12411</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1906</v>
+        <v>2253</v>
       </c>
       <c r="C5" t="n">
-        <v>4700</v>
+        <v>6201</v>
       </c>
       <c r="D5" t="n">
-        <v>7818</v>
+        <v>7113</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1330</v>
+        <v>1521</v>
       </c>
       <c r="C6" t="n">
-        <v>5737</v>
+        <v>7144</v>
       </c>
       <c r="D6" t="n">
-        <v>3246</v>
+        <v>2671</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>515</v>
+        <v>539</v>
       </c>
       <c r="C7" t="n">
-        <v>4688</v>
+        <v>5456</v>
       </c>
       <c r="D7" t="n">
-        <v>1084</v>
+        <v>926</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C8" t="n">
-        <v>2615</v>
+        <v>2811</v>
       </c>
       <c r="D8" t="n">
-        <v>483</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>1100</v>
+        <v>1061</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>376</v>
+        <v>344</v>
       </c>
       <c r="D10" t="n">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
         <v>64</v>
@@ -3753,7 +3753,7 @@
         <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4557</v>
+        <v>4930</v>
       </c>
       <c r="C2" t="n">
-        <v>5891</v>
+        <v>5311</v>
       </c>
       <c r="D2" t="n">
-        <v>16611</v>
+        <v>8359</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2111</v>
+        <v>2741</v>
       </c>
       <c r="C2" t="n">
-        <v>2776</v>
+        <v>4525</v>
       </c>
       <c r="D2" t="n">
-        <v>10507</v>
+        <v>11629</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2353</v>
+        <v>2776</v>
       </c>
       <c r="C3" t="n">
-        <v>3816</v>
+        <v>4287</v>
       </c>
       <c r="D3" t="n">
-        <v>11977</v>
+        <v>14026</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2730</v>
+        <v>3243</v>
       </c>
       <c r="C4" t="n">
-        <v>5034</v>
+        <v>6110</v>
       </c>
       <c r="D4" t="n">
-        <v>12839</v>
+        <v>12719</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1316</v>
+        <v>1467</v>
       </c>
       <c r="C5" t="n">
-        <v>7487</v>
+        <v>9648</v>
       </c>
       <c r="D5" t="n">
-        <v>7262</v>
+        <v>6498</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>475</v>
+        <v>498</v>
       </c>
       <c r="C6" t="n">
-        <v>5887</v>
+        <v>6747</v>
       </c>
       <c r="D6" t="n">
-        <v>2535</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>2562</v>
+        <v>2754</v>
       </c>
       <c r="D7" t="n">
-        <v>622</v>
+        <v>558</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>1078</v>
+        <v>1039</v>
       </c>
       <c r="D8" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>368</v>
+        <v>337</v>
       </c>
       <c r="D9" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D11" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
         <v>62</v>
@@ -4361,7 +4361,7 @@
         <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6230</v>
+        <v>6449</v>
       </c>
       <c r="C2" t="n">
-        <v>4762</v>
+        <v>4654</v>
       </c>
       <c r="D2" t="n">
-        <v>23545</v>
+        <v>10835</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1937</v>
+        <v>2095</v>
       </c>
       <c r="C3" t="n">
-        <v>2969</v>
+        <v>2719</v>
       </c>
       <c r="D3" t="n">
-        <v>3429</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3824</v>
+        <v>4686</v>
       </c>
       <c r="C2" t="n">
-        <v>4633</v>
+        <v>4673</v>
       </c>
       <c r="D2" t="n">
-        <v>35946</v>
+        <v>9746</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3350</v>
+        <v>3505</v>
       </c>
       <c r="C3" t="n">
-        <v>3435</v>
+        <v>3300</v>
       </c>
       <c r="D3" t="n">
-        <v>6556</v>
+        <v>3369</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>875</v>
+        <v>943</v>
       </c>
       <c r="C4" t="n">
-        <v>1784</v>
+        <v>1662</v>
       </c>
       <c r="D4" t="n">
-        <v>1872</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5036,7 +5036,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4165</v>
+        <v>4797</v>
       </c>
       <c r="C2" t="n">
-        <v>4261</v>
+        <v>4662</v>
       </c>
       <c r="D2" t="n">
-        <v>30106</v>
+        <v>25738</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2954</v>
+        <v>3367</v>
       </c>
       <c r="C3" t="n">
-        <v>3538</v>
+        <v>3510</v>
       </c>
       <c r="D3" t="n">
-        <v>10786</v>
+        <v>4146</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1793</v>
+        <v>1910</v>
       </c>
       <c r="C4" t="n">
-        <v>2682</v>
+        <v>2570</v>
       </c>
       <c r="D4" t="n">
-        <v>2714</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>412</v>
+        <v>446</v>
       </c>
       <c r="C5" t="n">
-        <v>1070</v>
+        <v>1018</v>
       </c>
       <c r="D5" t="n">
-        <v>1273</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11">
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
         <v>147</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4493</v>
+        <v>5006</v>
       </c>
       <c r="C2" t="n">
-        <v>3589</v>
+        <v>8209</v>
       </c>
       <c r="D2" t="n">
-        <v>25345</v>
+        <v>36432</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2899</v>
+        <v>3324</v>
       </c>
       <c r="C3" t="n">
-        <v>3403</v>
+        <v>3574</v>
       </c>
       <c r="D3" t="n">
-        <v>12963</v>
+        <v>7136</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2023</v>
+        <v>2227</v>
       </c>
       <c r="C4" t="n">
-        <v>3086</v>
+        <v>3030</v>
       </c>
       <c r="D4" t="n">
-        <v>4103</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>900</v>
+        <v>979</v>
       </c>
       <c r="C5" t="n">
-        <v>1873</v>
+        <v>1816</v>
       </c>
       <c r="D5" t="n">
-        <v>1471</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="C6" t="n">
-        <v>690</v>
+        <v>660</v>
       </c>
       <c r="D6" t="n">
-        <v>958</v>
+        <v>943</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
         <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -5563,7 +5563,7 @@
         <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
         <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
         <v>79</v>
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4681</v>
+        <v>6507</v>
       </c>
       <c r="C2" t="n">
-        <v>6247</v>
+        <v>8526</v>
       </c>
       <c r="D2" t="n">
-        <v>31649</v>
+        <v>34598</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2670</v>
+        <v>3027</v>
       </c>
       <c r="C3" t="n">
-        <v>2865</v>
+        <v>4902</v>
       </c>
       <c r="D3" t="n">
-        <v>13108</v>
+        <v>10428</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1518</v>
+        <v>1734</v>
       </c>
       <c r="C4" t="n">
-        <v>2647</v>
+        <v>2735</v>
       </c>
       <c r="D4" t="n">
-        <v>4848</v>
+        <v>2636</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>761</v>
+        <v>834</v>
       </c>
       <c r="C5" t="n">
-        <v>1837</v>
+        <v>1783</v>
       </c>
       <c r="D5" t="n">
-        <v>1545</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="C6" t="n">
-        <v>866</v>
+        <v>845</v>
       </c>
       <c r="D6" t="n">
-        <v>795</v>
+        <v>757</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C7" t="n">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>515</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9">
@@ -5854,10 +5854,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
         <v>268</v>
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>116</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
         <v>97</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4124</v>
+        <v>4728</v>
       </c>
       <c r="C2" t="n">
-        <v>3723</v>
+        <v>8122</v>
       </c>
       <c r="D2" t="n">
-        <v>25196</v>
+        <v>33356</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3053</v>
+        <v>3997</v>
       </c>
       <c r="C3" t="n">
-        <v>4188</v>
+        <v>6059</v>
       </c>
       <c r="D3" t="n">
-        <v>15385</v>
+        <v>13897</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1839</v>
+        <v>2101</v>
       </c>
       <c r="C4" t="n">
-        <v>2725</v>
+        <v>4009</v>
       </c>
       <c r="D4" t="n">
-        <v>6445</v>
+        <v>4201</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1011</v>
+        <v>1153</v>
       </c>
       <c r="C5" t="n">
-        <v>2280</v>
+        <v>2295</v>
       </c>
       <c r="D5" t="n">
-        <v>2163</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>483</v>
+        <v>523</v>
       </c>
       <c r="C6" t="n">
-        <v>1414</v>
+        <v>1383</v>
       </c>
       <c r="D6" t="n">
-        <v>919</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="C7" t="n">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="D7" t="n">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
@@ -6241,7 +6241,7 @@
         <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6255,7 +6255,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3091</v>
+        <v>5103</v>
       </c>
       <c r="C2" t="n">
-        <v>10190</v>
+        <v>5083</v>
       </c>
       <c r="D2" t="n">
-        <v>21344</v>
+        <v>28543</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2950</v>
+        <v>3593</v>
       </c>
       <c r="C3" t="n">
-        <v>3395</v>
+        <v>6225</v>
       </c>
       <c r="D3" t="n">
-        <v>15847</v>
+        <v>16009</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2115</v>
+        <v>2633</v>
       </c>
       <c r="C4" t="n">
-        <v>3511</v>
+        <v>5106</v>
       </c>
       <c r="D4" t="n">
-        <v>7903</v>
+        <v>5894</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1247</v>
+        <v>1423</v>
       </c>
       <c r="C5" t="n">
-        <v>2480</v>
+        <v>3201</v>
       </c>
       <c r="D5" t="n">
-        <v>2919</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>684</v>
+        <v>766</v>
       </c>
       <c r="C6" t="n">
-        <v>1849</v>
+        <v>1843</v>
       </c>
       <c r="D6" t="n">
-        <v>1133</v>
+        <v>915</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>285</v>
+        <v>308</v>
       </c>
       <c r="C7" t="n">
-        <v>1054</v>
+        <v>1033</v>
       </c>
       <c r="D7" t="n">
-        <v>615</v>
+        <v>597</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C8" t="n">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6535,7 +6535,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
         <v>122</v>
@@ -6566,7 +6566,7 @@
         <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6605,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_13_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_13_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6514</v>
+        <v>5674</v>
       </c>
       <c r="C2" t="n">
-        <v>7508</v>
+        <v>4319</v>
       </c>
       <c r="D2" t="n">
-        <v>26333</v>
+        <v>31228</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3530</v>
+        <v>3599</v>
       </c>
       <c r="C3" t="n">
-        <v>4966</v>
+        <v>4832</v>
       </c>
       <c r="D3" t="n">
-        <v>16787</v>
+        <v>15348</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2641</v>
+        <v>2734</v>
       </c>
       <c r="C4" t="n">
-        <v>5541</v>
+        <v>5798</v>
       </c>
       <c r="D4" t="n">
-        <v>7559</v>
+        <v>7700</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1758</v>
+        <v>1775</v>
       </c>
       <c r="C5" t="n">
-        <v>4121</v>
+        <v>5460</v>
       </c>
       <c r="D5" t="n">
-        <v>2524</v>
+        <v>2863</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>975</v>
+        <v>992</v>
       </c>
       <c r="C6" t="n">
-        <v>2482</v>
+        <v>3709</v>
       </c>
       <c r="D6" t="n">
-        <v>1074</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="C7" t="n">
-        <v>1437</v>
+        <v>2038</v>
       </c>
       <c r="D7" t="n">
-        <v>638</v>
+        <v>648</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C8" t="n">
-        <v>733</v>
+        <v>997</v>
       </c>
       <c r="D8" t="n">
-        <v>442</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>340</v>
+        <v>408</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -892,7 +892,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
         <v>215</v>
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6488</v>
+        <v>5580</v>
       </c>
       <c r="C2" t="n">
-        <v>12261</v>
+        <v>8277</v>
       </c>
       <c r="D2" t="n">
-        <v>28786</v>
+        <v>36525</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3985</v>
+        <v>3655</v>
       </c>
       <c r="C3" t="n">
-        <v>5399</v>
+        <v>4070</v>
       </c>
       <c r="D3" t="n">
-        <v>16957</v>
+        <v>16373</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2590</v>
+        <v>2647</v>
       </c>
       <c r="C4" t="n">
-        <v>5144</v>
+        <v>5176</v>
       </c>
       <c r="D4" t="n">
-        <v>8762</v>
+        <v>8566</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1897</v>
+        <v>1925</v>
       </c>
       <c r="C5" t="n">
-        <v>4663</v>
+        <v>5498</v>
       </c>
       <c r="D5" t="n">
-        <v>3268</v>
+        <v>3518</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="C6" t="n">
-        <v>3212</v>
+        <v>4394</v>
       </c>
       <c r="D6" t="n">
-        <v>1271</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="7">
@@ -1164,10 +1164,10 @@
         <v>614</v>
       </c>
       <c r="C7" t="n">
-        <v>1893</v>
+        <v>2757</v>
       </c>
       <c r="D7" t="n">
-        <v>699</v>
+        <v>719</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C8" t="n">
-        <v>1043</v>
+        <v>1415</v>
       </c>
       <c r="D8" t="n">
-        <v>461</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>502</v>
+        <v>640</v>
       </c>
       <c r="D9" t="n">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>266</v>
+        <v>290</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7100</v>
+        <v>6725</v>
       </c>
       <c r="C2" t="n">
-        <v>9782</v>
+        <v>8406</v>
       </c>
       <c r="D2" t="n">
-        <v>30265</v>
+        <v>29811</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4095</v>
+        <v>3644</v>
       </c>
       <c r="C3" t="n">
-        <v>7357</v>
+        <v>5101</v>
       </c>
       <c r="D3" t="n">
-        <v>17358</v>
+        <v>17743</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2692</v>
+        <v>2586</v>
       </c>
       <c r="C4" t="n">
-        <v>5152</v>
+        <v>4551</v>
       </c>
       <c r="D4" t="n">
-        <v>9754</v>
+        <v>9429</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1960</v>
+        <v>1963</v>
       </c>
       <c r="C5" t="n">
-        <v>4729</v>
+        <v>5250</v>
       </c>
       <c r="D5" t="n">
-        <v>3928</v>
+        <v>4055</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1356</v>
+        <v>1353</v>
       </c>
       <c r="C6" t="n">
-        <v>3795</v>
+        <v>4747</v>
       </c>
       <c r="D6" t="n">
-        <v>1541</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>765</v>
+        <v>754</v>
       </c>
       <c r="C7" t="n">
-        <v>2416</v>
+        <v>3370</v>
       </c>
       <c r="D7" t="n">
-        <v>763</v>
+        <v>804</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="C8" t="n">
-        <v>1373</v>
+        <v>1927</v>
       </c>
       <c r="D8" t="n">
-        <v>488</v>
+        <v>476</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>713</v>
+        <v>914</v>
       </c>
       <c r="D9" t="n">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>351</v>
+        <v>410</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1545,7 +1545,7 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D12" t="n">
         <v>164</v>
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6561</v>
+        <v>6226</v>
       </c>
       <c r="C2" t="n">
-        <v>6573</v>
+        <v>5850</v>
       </c>
       <c r="D2" t="n">
-        <v>24878</v>
+        <v>24700</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4910</v>
+        <v>4469</v>
       </c>
       <c r="C3" t="n">
-        <v>10342</v>
+        <v>7693</v>
       </c>
       <c r="D3" t="n">
-        <v>18899</v>
+        <v>19078</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1811</v>
+        <v>1813</v>
       </c>
       <c r="C4" t="n">
-        <v>7457</v>
+        <v>7486</v>
       </c>
       <c r="D4" t="n">
-        <v>9138</v>
+        <v>8958</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="C5" t="n">
-        <v>3719</v>
+        <v>4652</v>
       </c>
       <c r="D5" t="n">
-        <v>2603</v>
+        <v>2703</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>706</v>
+        <v>696</v>
       </c>
       <c r="C6" t="n">
-        <v>2367</v>
+        <v>3302</v>
       </c>
       <c r="D6" t="n">
-        <v>747</v>
+        <v>787</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="C7" t="n">
-        <v>1345</v>
+        <v>1888</v>
       </c>
       <c r="D7" t="n">
-        <v>478</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>698</v>
+        <v>895</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>343</v>
+        <v>401</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
         <v>160</v>
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3988</v>
+        <v>3852</v>
       </c>
       <c r="C2" t="n">
-        <v>2720</v>
+        <v>2591</v>
       </c>
       <c r="D2" t="n">
-        <v>17631</v>
+        <v>18530</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4871</v>
+        <v>4493</v>
       </c>
       <c r="C3" t="n">
-        <v>7797</v>
+        <v>6254</v>
       </c>
       <c r="D3" t="n">
-        <v>18623</v>
+        <v>18926</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2605</v>
+        <v>2430</v>
       </c>
       <c r="C4" t="n">
-        <v>8873</v>
+        <v>7639</v>
       </c>
       <c r="D4" t="n">
-        <v>10534</v>
+        <v>10228</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1396</v>
+        <v>1375</v>
       </c>
       <c r="C5" t="n">
-        <v>5399</v>
+        <v>5921</v>
       </c>
       <c r="D5" t="n">
-        <v>3389</v>
+        <v>3479</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>847</v>
+        <v>828</v>
       </c>
       <c r="C6" t="n">
-        <v>2991</v>
+        <v>3925</v>
       </c>
       <c r="D6" t="n">
-        <v>938</v>
+        <v>966</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="C7" t="n">
-        <v>1730</v>
+        <v>2427</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>508</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
-        <v>917</v>
+        <v>1178</v>
       </c>
       <c r="D8" t="n">
-        <v>341</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C9" t="n">
-        <v>397</v>
+        <v>448</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3748</v>
+        <v>3572</v>
       </c>
       <c r="C2" t="n">
-        <v>4741</v>
+        <v>7626</v>
       </c>
       <c r="D2" t="n">
-        <v>14845</v>
+        <v>24432</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3778</v>
+        <v>3552</v>
       </c>
       <c r="C3" t="n">
-        <v>4746</v>
+        <v>4059</v>
       </c>
       <c r="D3" t="n">
-        <v>17377</v>
+        <v>17600</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3096</v>
+        <v>2853</v>
       </c>
       <c r="C4" t="n">
-        <v>8151</v>
+        <v>6815</v>
       </c>
       <c r="D4" t="n">
-        <v>11432</v>
+        <v>11336</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1691</v>
+        <v>1612</v>
       </c>
       <c r="C5" t="n">
-        <v>7006</v>
+        <v>6589</v>
       </c>
       <c r="D5" t="n">
-        <v>4452</v>
+        <v>4409</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>988</v>
+        <v>964</v>
       </c>
       <c r="C6" t="n">
-        <v>4048</v>
+        <v>4807</v>
       </c>
       <c r="D6" t="n">
-        <v>1301</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="C7" t="n">
-        <v>2302</v>
+        <v>3057</v>
       </c>
       <c r="D7" t="n">
-        <v>581</v>
+        <v>565</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="C8" t="n">
-        <v>1260</v>
+        <v>1690</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>599</v>
+        <v>728</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2213</v>
+        <v>2153</v>
       </c>
       <c r="C2" t="n">
-        <v>2186</v>
+        <v>3642</v>
       </c>
       <c r="D2" t="n">
-        <v>10248</v>
+        <v>17068</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3667</v>
+        <v>3433</v>
       </c>
       <c r="C3" t="n">
-        <v>4592</v>
+        <v>5112</v>
       </c>
       <c r="D3" t="n">
-        <v>16676</v>
+        <v>17916</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3400</v>
+        <v>3136</v>
       </c>
       <c r="C4" t="n">
-        <v>7619</v>
+        <v>6454</v>
       </c>
       <c r="D4" t="n">
-        <v>12246</v>
+        <v>12119</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1752</v>
+        <v>1684</v>
       </c>
       <c r="C5" t="n">
-        <v>8320</v>
+        <v>7665</v>
       </c>
       <c r="D5" t="n">
-        <v>4810</v>
+        <v>4658</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>835</v>
+        <v>792</v>
       </c>
       <c r="C6" t="n">
-        <v>4894</v>
+        <v>5733</v>
       </c>
       <c r="D6" t="n">
-        <v>1271</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C7" t="n">
-        <v>2373</v>
+        <v>3150</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>567</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>982</v>
+        <v>1226</v>
       </c>
       <c r="D8" t="n">
-        <v>383</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3122</v>
+        <v>2717</v>
       </c>
       <c r="C2" t="n">
-        <v>4220</v>
+        <v>7711</v>
       </c>
       <c r="D2" t="n">
-        <v>14591</v>
+        <v>18507</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2618</v>
+        <v>2490</v>
       </c>
       <c r="C3" t="n">
-        <v>3096</v>
+        <v>3959</v>
       </c>
       <c r="D3" t="n">
-        <v>14681</v>
+        <v>16768</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3103</v>
+        <v>2877</v>
       </c>
       <c r="C4" t="n">
-        <v>6080</v>
+        <v>5750</v>
       </c>
       <c r="D4" t="n">
-        <v>12596</v>
+        <v>12641</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2143</v>
+        <v>2008</v>
       </c>
       <c r="C5" t="n">
-        <v>7910</v>
+        <v>7044</v>
       </c>
       <c r="D5" t="n">
-        <v>5852</v>
+        <v>5590</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1081</v>
+        <v>1016</v>
       </c>
       <c r="C6" t="n">
-        <v>6344</v>
+        <v>6535</v>
       </c>
       <c r="D6" t="n">
-        <v>1730</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="C7" t="n">
-        <v>3431</v>
+        <v>4223</v>
       </c>
       <c r="D7" t="n">
-        <v>671</v>
+        <v>658</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>1505</v>
+        <v>1928</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>394</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>517</v>
+        <v>596</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2332</v>
+        <v>1905</v>
       </c>
       <c r="C2" t="n">
-        <v>3219</v>
+        <v>4267</v>
       </c>
       <c r="D2" t="n">
-        <v>11424</v>
+        <v>13091</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2438</v>
+        <v>2245</v>
       </c>
       <c r="C3" t="n">
-        <v>3213</v>
+        <v>4918</v>
       </c>
       <c r="D3" t="n">
-        <v>13871</v>
+        <v>16225</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2727</v>
+        <v>2548</v>
       </c>
       <c r="C4" t="n">
-        <v>4896</v>
+        <v>5073</v>
       </c>
       <c r="D4" t="n">
-        <v>12614</v>
+        <v>12893</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2330</v>
+        <v>2172</v>
       </c>
       <c r="C5" t="n">
-        <v>7381</v>
+        <v>6708</v>
       </c>
       <c r="D5" t="n">
-        <v>6563</v>
+        <v>6218</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1269</v>
+        <v>1183</v>
       </c>
       <c r="C6" t="n">
-        <v>7092</v>
+        <v>6963</v>
       </c>
       <c r="D6" t="n">
-        <v>2099</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>292</v>
+        <v>269</v>
       </c>
       <c r="C7" t="n">
-        <v>4378</v>
+        <v>5054</v>
       </c>
       <c r="D7" t="n">
-        <v>764</v>
+        <v>734</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1959</v>
+        <v>2463</v>
       </c>
       <c r="D8" t="n">
-        <v>413</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>605</v>
+        <v>677</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
         <v>92</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
         <v>63</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3834</v>
+        <v>3302</v>
       </c>
       <c r="C2" t="n">
-        <v>7966</v>
+        <v>12459</v>
       </c>
       <c r="D2" t="n">
-        <v>15800</v>
+        <v>13314</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2019</v>
+        <v>1791</v>
       </c>
       <c r="C3" t="n">
-        <v>2855</v>
+        <v>4145</v>
       </c>
       <c r="D3" t="n">
-        <v>12689</v>
+        <v>14810</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2281</v>
+        <v>2123</v>
       </c>
       <c r="C4" t="n">
-        <v>4067</v>
+        <v>4902</v>
       </c>
       <c r="D4" t="n">
-        <v>12411</v>
+        <v>12980</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2253</v>
+        <v>2101</v>
       </c>
       <c r="C5" t="n">
-        <v>6201</v>
+        <v>5909</v>
       </c>
       <c r="D5" t="n">
-        <v>7113</v>
+        <v>6926</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1521</v>
+        <v>1409</v>
       </c>
       <c r="C6" t="n">
-        <v>7144</v>
+        <v>6806</v>
       </c>
       <c r="D6" t="n">
-        <v>2671</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>539</v>
+        <v>492</v>
       </c>
       <c r="C7" t="n">
-        <v>5456</v>
+        <v>5812</v>
       </c>
       <c r="D7" t="n">
-        <v>926</v>
+        <v>885</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>2811</v>
+        <v>3350</v>
       </c>
       <c r="D8" t="n">
-        <v>450</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>1061</v>
+        <v>1260</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
         <v>64</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4930</v>
+        <v>5990</v>
       </c>
       <c r="C2" t="n">
-        <v>5311</v>
+        <v>8912</v>
       </c>
       <c r="D2" t="n">
-        <v>8359</v>
+        <v>8568</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2741</v>
+        <v>2387</v>
       </c>
       <c r="C2" t="n">
-        <v>4525</v>
+        <v>7177</v>
       </c>
       <c r="D2" t="n">
-        <v>11629</v>
+        <v>9905</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2776</v>
+        <v>2477</v>
       </c>
       <c r="C3" t="n">
-        <v>4287</v>
+        <v>6372</v>
       </c>
       <c r="D3" t="n">
-        <v>14026</v>
+        <v>15835</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3243</v>
+        <v>3023</v>
       </c>
       <c r="C4" t="n">
-        <v>6110</v>
+        <v>6975</v>
       </c>
       <c r="D4" t="n">
-        <v>12719</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1467</v>
+        <v>1340</v>
       </c>
       <c r="C5" t="n">
-        <v>9648</v>
+        <v>9203</v>
       </c>
       <c r="D5" t="n">
-        <v>6498</v>
+        <v>6247</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>498</v>
+        <v>454</v>
       </c>
       <c r="C6" t="n">
-        <v>6747</v>
+        <v>6963</v>
       </c>
       <c r="D6" t="n">
-        <v>2098</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C7" t="n">
-        <v>2754</v>
+        <v>3283</v>
       </c>
       <c r="D7" t="n">
-        <v>558</v>
+        <v>541</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>1039</v>
+        <v>1234</v>
       </c>
       <c r="D8" t="n">
-        <v>303</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
         <v>62</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6449</v>
+        <v>6723</v>
       </c>
       <c r="C2" t="n">
-        <v>4654</v>
+        <v>7509</v>
       </c>
       <c r="D2" t="n">
-        <v>10835</v>
+        <v>20632</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2095</v>
+        <v>2545</v>
       </c>
       <c r="C3" t="n">
-        <v>2719</v>
+        <v>4491</v>
       </c>
       <c r="D3" t="n">
-        <v>2043</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4557,7 +4557,7 @@
         <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4574,7 +4574,7 @@
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4686</v>
+        <v>4507</v>
       </c>
       <c r="C2" t="n">
-        <v>4673</v>
+        <v>6028</v>
       </c>
       <c r="D2" t="n">
-        <v>9746</v>
+        <v>23134</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3505</v>
+        <v>3805</v>
       </c>
       <c r="C3" t="n">
-        <v>3300</v>
+        <v>5345</v>
       </c>
       <c r="D3" t="n">
-        <v>3369</v>
+        <v>5042</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>943</v>
+        <v>1140</v>
       </c>
       <c r="C4" t="n">
-        <v>1662</v>
+        <v>2675</v>
       </c>
       <c r="D4" t="n">
-        <v>1593</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4797</v>
+        <v>5430</v>
       </c>
       <c r="C2" t="n">
-        <v>4662</v>
+        <v>7170</v>
       </c>
       <c r="D2" t="n">
-        <v>25738</v>
+        <v>22589</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3367</v>
+        <v>3420</v>
       </c>
       <c r="C3" t="n">
-        <v>3510</v>
+        <v>5000</v>
       </c>
       <c r="D3" t="n">
-        <v>4146</v>
+        <v>7573</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1910</v>
+        <v>2103</v>
       </c>
       <c r="C4" t="n">
-        <v>2570</v>
+        <v>4080</v>
       </c>
       <c r="D4" t="n">
-        <v>1870</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>446</v>
+        <v>518</v>
       </c>
       <c r="C5" t="n">
-        <v>1018</v>
+        <v>1560</v>
       </c>
       <c r="D5" t="n">
-        <v>1228</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
         <v>147</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5336,7 +5336,7 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5006</v>
+        <v>5567</v>
       </c>
       <c r="C2" t="n">
-        <v>8209</v>
+        <v>13979</v>
       </c>
       <c r="D2" t="n">
-        <v>36432</v>
+        <v>33581</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3324</v>
+        <v>3571</v>
       </c>
       <c r="C3" t="n">
-        <v>3574</v>
+        <v>5324</v>
       </c>
       <c r="D3" t="n">
-        <v>7136</v>
+        <v>9322</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2227</v>
+        <v>2325</v>
       </c>
       <c r="C4" t="n">
-        <v>3030</v>
+        <v>4489</v>
       </c>
       <c r="D4" t="n">
-        <v>2210</v>
+        <v>3122</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>979</v>
+        <v>1079</v>
       </c>
       <c r="C5" t="n">
-        <v>1816</v>
+        <v>2833</v>
       </c>
       <c r="D5" t="n">
-        <v>1307</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="C6" t="n">
-        <v>660</v>
+        <v>924</v>
       </c>
       <c r="D6" t="n">
-        <v>943</v>
+        <v>949</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
         <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5563,7 +5563,7 @@
         <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5619,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6507</v>
+        <v>6384</v>
       </c>
       <c r="C2" t="n">
-        <v>8526</v>
+        <v>7794</v>
       </c>
       <c r="D2" t="n">
-        <v>34598</v>
+        <v>29068</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3027</v>
+        <v>3281</v>
       </c>
       <c r="C3" t="n">
-        <v>4902</v>
+        <v>7919</v>
       </c>
       <c r="D3" t="n">
-        <v>10428</v>
+        <v>11621</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1734</v>
+        <v>1805</v>
       </c>
       <c r="C4" t="n">
-        <v>2735</v>
+        <v>4008</v>
       </c>
       <c r="D4" t="n">
-        <v>2636</v>
+        <v>3628</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>834</v>
+        <v>882</v>
       </c>
       <c r="C5" t="n">
-        <v>1783</v>
+        <v>2694</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>294</v>
+        <v>321</v>
       </c>
       <c r="C6" t="n">
-        <v>845</v>
+        <v>1257</v>
       </c>
       <c r="D6" t="n">
-        <v>757</v>
+        <v>773</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C7" t="n">
-        <v>324</v>
+        <v>398</v>
       </c>
       <c r="D7" t="n">
-        <v>525</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>365</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D9" t="n">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5916,7 +5916,7 @@
         <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4728</v>
+        <v>5425</v>
       </c>
       <c r="C2" t="n">
-        <v>8122</v>
+        <v>5941</v>
       </c>
       <c r="D2" t="n">
-        <v>33356</v>
+        <v>25051</v>
       </c>
     </row>
     <row r="3">
@@ -6084,10 +6084,10 @@
         <v>3997</v>
       </c>
       <c r="C3" t="n">
-        <v>6059</v>
+        <v>6754</v>
       </c>
       <c r="D3" t="n">
-        <v>13897</v>
+        <v>13696</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2101</v>
+        <v>2222</v>
       </c>
       <c r="C4" t="n">
-        <v>4009</v>
+        <v>6252</v>
       </c>
       <c r="D4" t="n">
-        <v>4201</v>
+        <v>5129</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1153</v>
+        <v>1184</v>
       </c>
       <c r="C5" t="n">
-        <v>2295</v>
+        <v>3368</v>
       </c>
       <c r="D5" t="n">
-        <v>1423</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>523</v>
+        <v>556</v>
       </c>
       <c r="C6" t="n">
-        <v>1383</v>
+        <v>2055</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>861</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="C7" t="n">
-        <v>625</v>
+        <v>877</v>
       </c>
       <c r="D7" t="n">
-        <v>565</v>
+        <v>551</v>
       </c>
     </row>
     <row r="8">
@@ -6154,10 +6154,10 @@
         <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>278</v>
+        <v>317</v>
       </c>
       <c r="D8" t="n">
-        <v>391</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>279</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6238,10 +6238,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5103</v>
+        <v>5003</v>
       </c>
       <c r="C2" t="n">
-        <v>5083</v>
+        <v>5567</v>
       </c>
       <c r="D2" t="n">
-        <v>28543</v>
+        <v>26456</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3593</v>
+        <v>3854</v>
       </c>
       <c r="C3" t="n">
-        <v>6225</v>
+        <v>5479</v>
       </c>
       <c r="D3" t="n">
-        <v>16009</v>
+        <v>14658</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2633</v>
+        <v>2656</v>
       </c>
       <c r="C4" t="n">
-        <v>5106</v>
+        <v>6401</v>
       </c>
       <c r="D4" t="n">
-        <v>5894</v>
+        <v>6486</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1423</v>
+        <v>1472</v>
       </c>
       <c r="C5" t="n">
-        <v>3201</v>
+        <v>4848</v>
       </c>
       <c r="D5" t="n">
-        <v>1913</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>766</v>
+        <v>785</v>
       </c>
       <c r="C6" t="n">
-        <v>1843</v>
+        <v>2712</v>
       </c>
       <c r="D6" t="n">
-        <v>915</v>
+        <v>983</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="C7" t="n">
-        <v>1033</v>
+        <v>1468</v>
       </c>
       <c r="D7" t="n">
-        <v>597</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>458</v>
+        <v>596</v>
       </c>
       <c r="D8" t="n">
-        <v>417</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6605,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_13_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_13_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5674</v>
+        <v>727</v>
       </c>
       <c r="C2" t="n">
-        <v>4319</v>
+        <v>2917</v>
       </c>
       <c r="D2" t="n">
-        <v>31228</v>
+        <v>15428</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3599</v>
+        <v>1450</v>
       </c>
       <c r="C3" t="n">
-        <v>4832</v>
+        <v>5990</v>
       </c>
       <c r="D3" t="n">
-        <v>15348</v>
+        <v>14114</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2734</v>
+        <v>1030</v>
       </c>
       <c r="C4" t="n">
-        <v>5798</v>
+        <v>7301</v>
       </c>
       <c r="D4" t="n">
-        <v>7700</v>
+        <v>6279</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1775</v>
+        <v>486</v>
       </c>
       <c r="C5" t="n">
-        <v>5460</v>
+        <v>5071</v>
       </c>
       <c r="D5" t="n">
-        <v>2863</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>992</v>
+        <v>218</v>
       </c>
       <c r="C6" t="n">
-        <v>3709</v>
+        <v>2346</v>
       </c>
       <c r="D6" t="n">
-        <v>1178</v>
+        <v>754</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>473</v>
+        <v>99</v>
       </c>
       <c r="C7" t="n">
-        <v>2038</v>
+        <v>862</v>
       </c>
       <c r="D7" t="n">
-        <v>648</v>
+        <v>482</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>175</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>997</v>
+        <v>361</v>
       </c>
       <c r="D8" t="n">
-        <v>430</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>408</v>
+        <v>282</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>141</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5580</v>
+        <v>446</v>
       </c>
       <c r="C2" t="n">
-        <v>8277</v>
+        <v>8925</v>
       </c>
       <c r="D2" t="n">
-        <v>36525</v>
+        <v>20853</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3655</v>
+        <v>940</v>
       </c>
       <c r="C3" t="n">
-        <v>4070</v>
+        <v>3802</v>
       </c>
       <c r="D3" t="n">
-        <v>16373</v>
+        <v>13320</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2647</v>
+        <v>1068</v>
       </c>
       <c r="C4" t="n">
-        <v>5176</v>
+        <v>6501</v>
       </c>
       <c r="D4" t="n">
-        <v>8566</v>
+        <v>7517</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1925</v>
+        <v>646</v>
       </c>
       <c r="C5" t="n">
-        <v>5498</v>
+        <v>6121</v>
       </c>
       <c r="D5" t="n">
-        <v>3518</v>
+        <v>2688</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1209</v>
+        <v>308</v>
       </c>
       <c r="C6" t="n">
-        <v>4394</v>
+        <v>3703</v>
       </c>
       <c r="D6" t="n">
-        <v>1393</v>
+        <v>949</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>614</v>
+        <v>134</v>
       </c>
       <c r="C7" t="n">
-        <v>2757</v>
+        <v>1582</v>
       </c>
       <c r="D7" t="n">
-        <v>719</v>
+        <v>519</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>259</v>
+        <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>1415</v>
+        <v>593</v>
       </c>
       <c r="D8" t="n">
-        <v>451</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>640</v>
+        <v>317</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>290</v>
+        <v>242</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6725</v>
+        <v>236</v>
       </c>
       <c r="C2" t="n">
-        <v>8406</v>
+        <v>3743</v>
       </c>
       <c r="D2" t="n">
-        <v>29811</v>
+        <v>14206</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3644</v>
+        <v>770</v>
       </c>
       <c r="C3" t="n">
-        <v>5101</v>
+        <v>5617</v>
       </c>
       <c r="D3" t="n">
-        <v>17743</v>
+        <v>13882</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2586</v>
+        <v>1151</v>
       </c>
       <c r="C4" t="n">
-        <v>4551</v>
+        <v>5953</v>
       </c>
       <c r="D4" t="n">
-        <v>9429</v>
+        <v>8262</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1963</v>
+        <v>655</v>
       </c>
       <c r="C5" t="n">
-        <v>5250</v>
+        <v>6977</v>
       </c>
       <c r="D5" t="n">
-        <v>4055</v>
+        <v>3024</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1353</v>
+        <v>260</v>
       </c>
       <c r="C6" t="n">
-        <v>4747</v>
+        <v>4693</v>
       </c>
       <c r="D6" t="n">
-        <v>1646</v>
+        <v>963</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>754</v>
+        <v>71</v>
       </c>
       <c r="C7" t="n">
-        <v>3370</v>
+        <v>1503</v>
       </c>
       <c r="D7" t="n">
-        <v>804</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>346</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1927</v>
+        <v>519</v>
       </c>
       <c r="D8" t="n">
-        <v>476</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>136</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>914</v>
+        <v>237</v>
       </c>
       <c r="D9" t="n">
-        <v>333</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>410</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>218</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6226</v>
+        <v>355</v>
       </c>
       <c r="C2" t="n">
-        <v>5850</v>
+        <v>7353</v>
       </c>
       <c r="D2" t="n">
-        <v>24700</v>
+        <v>16358</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4469</v>
+        <v>454</v>
       </c>
       <c r="C3" t="n">
-        <v>7693</v>
+        <v>4103</v>
       </c>
       <c r="D3" t="n">
-        <v>19078</v>
+        <v>13087</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1813</v>
+        <v>877</v>
       </c>
       <c r="C4" t="n">
-        <v>7486</v>
+        <v>5708</v>
       </c>
       <c r="D4" t="n">
-        <v>8958</v>
+        <v>8981</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1250</v>
+        <v>779</v>
       </c>
       <c r="C5" t="n">
-        <v>4652</v>
+        <v>6387</v>
       </c>
       <c r="D5" t="n">
-        <v>2703</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>696</v>
+        <v>383</v>
       </c>
       <c r="C6" t="n">
-        <v>3302</v>
+        <v>5811</v>
       </c>
       <c r="D6" t="n">
-        <v>787</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>319</v>
+        <v>123</v>
       </c>
       <c r="C7" t="n">
-        <v>1888</v>
+        <v>2938</v>
       </c>
       <c r="D7" t="n">
-        <v>466</v>
+        <v>601</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>895</v>
+        <v>924</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>401</v>
+        <v>346</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3852</v>
+        <v>248</v>
       </c>
       <c r="C2" t="n">
-        <v>2591</v>
+        <v>3990</v>
       </c>
       <c r="D2" t="n">
-        <v>18530</v>
+        <v>12595</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4493</v>
+        <v>365</v>
       </c>
       <c r="C3" t="n">
-        <v>6254</v>
+        <v>5048</v>
       </c>
       <c r="D3" t="n">
-        <v>18926</v>
+        <v>12778</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2430</v>
+        <v>680</v>
       </c>
       <c r="C4" t="n">
-        <v>7639</v>
+        <v>5014</v>
       </c>
       <c r="D4" t="n">
-        <v>10228</v>
+        <v>9511</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1375</v>
+        <v>799</v>
       </c>
       <c r="C5" t="n">
-        <v>5921</v>
+        <v>6219</v>
       </c>
       <c r="D5" t="n">
-        <v>3479</v>
+        <v>4355</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>828</v>
+        <v>463</v>
       </c>
       <c r="C6" t="n">
-        <v>3925</v>
+        <v>6255</v>
       </c>
       <c r="D6" t="n">
-        <v>966</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>298</v>
+        <v>138</v>
       </c>
       <c r="C7" t="n">
-        <v>2427</v>
+        <v>3983</v>
       </c>
       <c r="D7" t="n">
-        <v>508</v>
+        <v>663</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1178</v>
+        <v>1432</v>
       </c>
       <c r="D8" t="n">
-        <v>335</v>
+        <v>479</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="D9" t="n">
-        <v>254</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3572</v>
+        <v>236</v>
       </c>
       <c r="C2" t="n">
-        <v>7626</v>
+        <v>14329</v>
       </c>
       <c r="D2" t="n">
-        <v>24432</v>
+        <v>21672</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3552</v>
+        <v>266</v>
       </c>
       <c r="C3" t="n">
-        <v>4059</v>
+        <v>4019</v>
       </c>
       <c r="D3" t="n">
-        <v>17600</v>
+        <v>11894</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2853</v>
+        <v>486</v>
       </c>
       <c r="C4" t="n">
-        <v>6815</v>
+        <v>4926</v>
       </c>
       <c r="D4" t="n">
-        <v>11336</v>
+        <v>9755</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1612</v>
+        <v>700</v>
       </c>
       <c r="C5" t="n">
-        <v>6589</v>
+        <v>5594</v>
       </c>
       <c r="D5" t="n">
-        <v>4409</v>
+        <v>5014</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>964</v>
+        <v>549</v>
       </c>
       <c r="C6" t="n">
-        <v>4807</v>
+        <v>6180</v>
       </c>
       <c r="D6" t="n">
-        <v>1315</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>443</v>
+        <v>227</v>
       </c>
       <c r="C7" t="n">
-        <v>3057</v>
+        <v>4977</v>
       </c>
       <c r="D7" t="n">
-        <v>565</v>
+        <v>779</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>150</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>1690</v>
+        <v>2445</v>
       </c>
       <c r="D8" t="n">
-        <v>353</v>
+        <v>497</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>728</v>
+        <v>812</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>386</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2153</v>
+        <v>160</v>
       </c>
       <c r="C2" t="n">
-        <v>3642</v>
+        <v>7566</v>
       </c>
       <c r="D2" t="n">
-        <v>17068</v>
+        <v>15777</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3433</v>
+        <v>391</v>
       </c>
       <c r="C3" t="n">
-        <v>5112</v>
+        <v>7138</v>
       </c>
       <c r="D3" t="n">
-        <v>17916</v>
+        <v>13446</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3136</v>
+        <v>878</v>
       </c>
       <c r="C4" t="n">
-        <v>6454</v>
+        <v>6849</v>
       </c>
       <c r="D4" t="n">
-        <v>12119</v>
+        <v>10003</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1684</v>
+        <v>552</v>
       </c>
       <c r="C5" t="n">
-        <v>7665</v>
+        <v>8469</v>
       </c>
       <c r="D5" t="n">
-        <v>4658</v>
+        <v>4639</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>792</v>
+        <v>209</v>
       </c>
       <c r="C6" t="n">
-        <v>5733</v>
+        <v>6330</v>
       </c>
       <c r="D6" t="n">
-        <v>1285</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>138</v>
+        <v>66</v>
       </c>
       <c r="C7" t="n">
-        <v>3150</v>
+        <v>2396</v>
       </c>
       <c r="D7" t="n">
-        <v>567</v>
+        <v>601</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>1226</v>
+        <v>795</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2717</v>
+        <v>72</v>
       </c>
       <c r="C2" t="n">
-        <v>7711</v>
+        <v>3576</v>
       </c>
       <c r="D2" t="n">
-        <v>18507</v>
+        <v>11186</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2490</v>
+        <v>250</v>
       </c>
       <c r="C3" t="n">
-        <v>3959</v>
+        <v>6477</v>
       </c>
       <c r="D3" t="n">
-        <v>16768</v>
+        <v>12817</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2877</v>
+        <v>556</v>
       </c>
       <c r="C4" t="n">
-        <v>5750</v>
+        <v>6634</v>
       </c>
       <c r="D4" t="n">
-        <v>12641</v>
+        <v>9863</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2008</v>
+        <v>496</v>
       </c>
       <c r="C5" t="n">
-        <v>7044</v>
+        <v>6776</v>
       </c>
       <c r="D5" t="n">
-        <v>5590</v>
+        <v>4875</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1016</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>6535</v>
+        <v>6005</v>
       </c>
       <c r="D6" t="n">
-        <v>1721</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>298</v>
+        <v>53</v>
       </c>
       <c r="C7" t="n">
-        <v>4223</v>
+        <v>2932</v>
       </c>
       <c r="D7" t="n">
-        <v>658</v>
+        <v>583</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>1928</v>
+        <v>906</v>
       </c>
       <c r="D8" t="n">
-        <v>394</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>596</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>127</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1905</v>
+        <v>153</v>
       </c>
       <c r="C2" t="n">
-        <v>4267</v>
+        <v>8440</v>
       </c>
       <c r="D2" t="n">
-        <v>13091</v>
+        <v>10425</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2245</v>
+        <v>140</v>
       </c>
       <c r="C3" t="n">
-        <v>4918</v>
+        <v>4304</v>
       </c>
       <c r="D3" t="n">
-        <v>16225</v>
+        <v>11666</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2548</v>
+        <v>365</v>
       </c>
       <c r="C4" t="n">
-        <v>5073</v>
+        <v>6410</v>
       </c>
       <c r="D4" t="n">
-        <v>12893</v>
+        <v>10101</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2172</v>
+        <v>478</v>
       </c>
       <c r="C5" t="n">
-        <v>6708</v>
+        <v>6625</v>
       </c>
       <c r="D5" t="n">
-        <v>6218</v>
+        <v>5588</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1183</v>
+        <v>302</v>
       </c>
       <c r="C6" t="n">
-        <v>6963</v>
+        <v>6325</v>
       </c>
       <c r="D6" t="n">
-        <v>2085</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>269</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>5054</v>
+        <v>4465</v>
       </c>
       <c r="D7" t="n">
-        <v>734</v>
+        <v>755</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>2463</v>
+        <v>1847</v>
       </c>
       <c r="D8" t="n">
-        <v>406</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>677</v>
+        <v>556</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3302</v>
+        <v>88</v>
       </c>
       <c r="C2" t="n">
-        <v>12459</v>
+        <v>8514</v>
       </c>
       <c r="D2" t="n">
-        <v>13314</v>
+        <v>14362</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1791</v>
+        <v>120</v>
       </c>
       <c r="C3" t="n">
-        <v>4145</v>
+        <v>5494</v>
       </c>
       <c r="D3" t="n">
-        <v>14810</v>
+        <v>10684</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2123</v>
+        <v>234</v>
       </c>
       <c r="C4" t="n">
-        <v>4902</v>
+        <v>5225</v>
       </c>
       <c r="D4" t="n">
-        <v>12980</v>
+        <v>10064</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2101</v>
+        <v>392</v>
       </c>
       <c r="C5" t="n">
-        <v>5909</v>
+        <v>6384</v>
       </c>
       <c r="D5" t="n">
-        <v>6926</v>
+        <v>6154</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1409</v>
+        <v>349</v>
       </c>
       <c r="C6" t="n">
-        <v>6806</v>
+        <v>6338</v>
       </c>
       <c r="D6" t="n">
-        <v>2574</v>
+        <v>2677</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>492</v>
+        <v>166</v>
       </c>
       <c r="C7" t="n">
-        <v>5812</v>
+        <v>5319</v>
       </c>
       <c r="D7" t="n">
-        <v>885</v>
+        <v>975</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>3350</v>
+        <v>3000</v>
       </c>
       <c r="D8" t="n">
-        <v>437</v>
+        <v>414</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>1260</v>
+        <v>1099</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>222</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>358</v>
+        <v>338</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>155</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5990</v>
+        <v>3334</v>
       </c>
       <c r="C2" t="n">
-        <v>8912</v>
+        <v>14816</v>
       </c>
       <c r="D2" t="n">
-        <v>8568</v>
+        <v>11806</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2387</v>
+        <v>397</v>
       </c>
       <c r="C2" t="n">
-        <v>7177</v>
+        <v>9271</v>
       </c>
       <c r="D2" t="n">
-        <v>9905</v>
+        <v>19536</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2477</v>
+        <v>89</v>
       </c>
       <c r="C3" t="n">
-        <v>6372</v>
+        <v>5996</v>
       </c>
       <c r="D3" t="n">
-        <v>15835</v>
+        <v>10453</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3023</v>
+        <v>165</v>
       </c>
       <c r="C4" t="n">
-        <v>6975</v>
+        <v>5237</v>
       </c>
       <c r="D4" t="n">
-        <v>13250</v>
+        <v>9853</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1340</v>
+        <v>305</v>
       </c>
       <c r="C5" t="n">
-        <v>9203</v>
+        <v>5689</v>
       </c>
       <c r="D5" t="n">
-        <v>6247</v>
+        <v>6470</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>454</v>
+        <v>340</v>
       </c>
       <c r="C6" t="n">
-        <v>6963</v>
+        <v>6299</v>
       </c>
       <c r="D6" t="n">
-        <v>2015</v>
+        <v>3142</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>92</v>
+        <v>215</v>
       </c>
       <c r="C7" t="n">
-        <v>3283</v>
+        <v>5736</v>
       </c>
       <c r="D7" t="n">
-        <v>541</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="C8" t="n">
-        <v>1234</v>
+        <v>3878</v>
       </c>
       <c r="D8" t="n">
-        <v>293</v>
+        <v>486</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>350</v>
+        <v>1825</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>610</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>88</v>
+        <v>204</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6723</v>
+        <v>2784</v>
       </c>
       <c r="C2" t="n">
-        <v>7509</v>
+        <v>9008</v>
       </c>
       <c r="D2" t="n">
-        <v>20632</v>
+        <v>24618</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2545</v>
+        <v>1077</v>
       </c>
       <c r="C3" t="n">
-        <v>4491</v>
+        <v>5850</v>
       </c>
       <c r="D3" t="n">
-        <v>2078</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4507</v>
+        <v>2566</v>
       </c>
       <c r="C2" t="n">
-        <v>6028</v>
+        <v>5328</v>
       </c>
       <c r="D2" t="n">
-        <v>23134</v>
+        <v>19339</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3805</v>
+        <v>1624</v>
       </c>
       <c r="C3" t="n">
-        <v>5345</v>
+        <v>6705</v>
       </c>
       <c r="D3" t="n">
-        <v>5042</v>
+        <v>5999</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1140</v>
+        <v>524</v>
       </c>
       <c r="C4" t="n">
-        <v>2675</v>
+        <v>3643</v>
       </c>
       <c r="D4" t="n">
-        <v>1600</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5430</v>
+        <v>1812</v>
       </c>
       <c r="C2" t="n">
-        <v>7170</v>
+        <v>5068</v>
       </c>
       <c r="D2" t="n">
-        <v>22589</v>
+        <v>20921</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3420</v>
+        <v>1731</v>
       </c>
       <c r="C3" t="n">
-        <v>5000</v>
+        <v>5088</v>
       </c>
       <c r="D3" t="n">
-        <v>7573</v>
+        <v>7798</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2103</v>
+        <v>942</v>
       </c>
       <c r="C4" t="n">
-        <v>4080</v>
+        <v>5389</v>
       </c>
       <c r="D4" t="n">
-        <v>2212</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>518</v>
+        <v>271</v>
       </c>
       <c r="C5" t="n">
-        <v>1560</v>
+        <v>2182</v>
       </c>
       <c r="D5" t="n">
-        <v>1223</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>263</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>115</v>
       </c>
       <c r="C7" t="n">
-        <v>403</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>284</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5567</v>
+        <v>2131</v>
       </c>
       <c r="C2" t="n">
-        <v>13979</v>
+        <v>5553</v>
       </c>
       <c r="D2" t="n">
-        <v>33581</v>
+        <v>22933</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3571</v>
+        <v>1462</v>
       </c>
       <c r="C3" t="n">
-        <v>5324</v>
+        <v>4394</v>
       </c>
       <c r="D3" t="n">
-        <v>9322</v>
+        <v>9336</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2325</v>
+        <v>1148</v>
       </c>
       <c r="C4" t="n">
-        <v>4489</v>
+        <v>5106</v>
       </c>
       <c r="D4" t="n">
-        <v>3122</v>
+        <v>3372</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1079</v>
+        <v>512</v>
       </c>
       <c r="C5" t="n">
-        <v>2833</v>
+        <v>3891</v>
       </c>
       <c r="D5" t="n">
-        <v>1344</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>285</v>
+        <v>173</v>
       </c>
       <c r="C6" t="n">
-        <v>924</v>
+        <v>1273</v>
       </c>
       <c r="D6" t="n">
-        <v>949</v>
+        <v>839</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>353</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>248</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6384</v>
+        <v>1743</v>
       </c>
       <c r="C2" t="n">
-        <v>7794</v>
+        <v>5846</v>
       </c>
       <c r="D2" t="n">
-        <v>29068</v>
+        <v>24476</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3281</v>
+        <v>1456</v>
       </c>
       <c r="C3" t="n">
-        <v>7919</v>
+        <v>4343</v>
       </c>
       <c r="D3" t="n">
-        <v>11621</v>
+        <v>10745</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1805</v>
+        <v>1110</v>
       </c>
       <c r="C4" t="n">
-        <v>4008</v>
+        <v>4617</v>
       </c>
       <c r="D4" t="n">
-        <v>3628</v>
+        <v>4357</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>882</v>
+        <v>709</v>
       </c>
       <c r="C5" t="n">
-        <v>2694</v>
+        <v>4439</v>
       </c>
       <c r="D5" t="n">
-        <v>1293</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="C6" t="n">
-        <v>1257</v>
+        <v>2566</v>
       </c>
       <c r="D6" t="n">
-        <v>773</v>
+        <v>906</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="C7" t="n">
-        <v>398</v>
+        <v>774</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>621</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>298</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>275</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>172</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5425</v>
+        <v>1450</v>
       </c>
       <c r="C2" t="n">
-        <v>5941</v>
+        <v>9509</v>
       </c>
       <c r="D2" t="n">
-        <v>25051</v>
+        <v>28559</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3997</v>
+        <v>1320</v>
       </c>
       <c r="C3" t="n">
-        <v>6754</v>
+        <v>4433</v>
       </c>
       <c r="D3" t="n">
-        <v>13696</v>
+        <v>11983</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2222</v>
+        <v>1081</v>
       </c>
       <c r="C4" t="n">
-        <v>6252</v>
+        <v>4339</v>
       </c>
       <c r="D4" t="n">
-        <v>5129</v>
+        <v>5328</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1184</v>
+        <v>783</v>
       </c>
       <c r="C5" t="n">
-        <v>3368</v>
+        <v>4433</v>
       </c>
       <c r="D5" t="n">
-        <v>1689</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>556</v>
+        <v>435</v>
       </c>
       <c r="C6" t="n">
-        <v>2055</v>
+        <v>3420</v>
       </c>
       <c r="D6" t="n">
-        <v>861</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="C7" t="n">
-        <v>877</v>
+        <v>1599</v>
       </c>
       <c r="D7" t="n">
-        <v>551</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>317</v>
+        <v>504</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>284</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>240</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>144</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5003</v>
+        <v>1373</v>
       </c>
       <c r="C2" t="n">
-        <v>5567</v>
+        <v>5933</v>
       </c>
       <c r="D2" t="n">
-        <v>26456</v>
+        <v>22391</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3854</v>
+        <v>1831</v>
       </c>
       <c r="C3" t="n">
-        <v>5479</v>
+        <v>7387</v>
       </c>
       <c r="D3" t="n">
-        <v>14658</v>
+        <v>13442</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2656</v>
+        <v>723</v>
       </c>
       <c r="C4" t="n">
-        <v>6401</v>
+        <v>6963</v>
       </c>
       <c r="D4" t="n">
-        <v>6486</v>
+        <v>4949</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1472</v>
+        <v>401</v>
       </c>
       <c r="C5" t="n">
-        <v>4848</v>
+        <v>3351</v>
       </c>
       <c r="D5" t="n">
-        <v>2265</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>785</v>
+        <v>164</v>
       </c>
       <c r="C6" t="n">
-        <v>2712</v>
+        <v>1567</v>
       </c>
       <c r="D6" t="n">
-        <v>983</v>
+        <v>645</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>320</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>1468</v>
+        <v>493</v>
       </c>
       <c r="D7" t="n">
-        <v>600</v>
+        <v>446</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>596</v>
+        <v>278</v>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>260</v>
+        <v>235</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6518,10 +6518,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
         <v>158</v>
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>144</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
